--- a/overall pp analysis.xlsx
+++ b/overall pp analysis.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22476" windowHeight="9048" firstSheet="1" activeTab="5"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22476" windowHeight="9048" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="pp1_motor sequence_2025-10-01_2" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4070" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4076" uniqueCount="62">
   <si>
     <t>pos</t>
   </si>
@@ -198,6 +198,18 @@
   </si>
   <si>
     <t>random</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mean rt </t>
+  </si>
+  <si>
+    <t xml:space="preserve">difference </t>
+  </si>
+  <si>
+    <t xml:space="preserve">difference rt </t>
+  </si>
+  <si>
+    <t>difference</t>
   </si>
 </sst>
 </file>
@@ -841,29 +853,18 @@
               <a:buFontTx/>
               <a:buNone/>
               <a:tabLst/>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:defRPr>
                 <a:solidFill>
                   <a:sysClr val="window" lastClr="FFFFFF">
                     <a:lumMod val="95000"/>
                   </a:sysClr>
                 </a:solidFill>
-                <a:effectLst>
-                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                    <a:prstClr val="black">
-                      <a:alpha val="40000"/>
-                    </a:prstClr>
-                  </a:outerShdw>
-                </a:effectLst>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2262,7 +2263,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2379,7 +2379,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -2454,7 +2453,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2616,22 +2614,12 @@
               <a:buFontTx/>
               <a:buNone/>
               <a:tabLst/>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:defRPr>
                 <a:solidFill>
                   <a:sysClr val="window" lastClr="FFFFFF">
                     <a:lumMod val="95000"/>
                   </a:sysClr>
                 </a:solidFill>
-                <a:effectLst>
-                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                    <a:prstClr val="black">
-                      <a:alpha val="40000"/>
-                    </a:prstClr>
-                  </a:outerShdw>
-                </a:effectLst>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -4386,22 +4374,12 @@
               <a:buFontTx/>
               <a:buNone/>
               <a:tabLst/>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:defRPr>
                 <a:solidFill>
                   <a:sysClr val="window" lastClr="FFFFFF">
                     <a:lumMod val="95000"/>
                   </a:sysClr>
                 </a:solidFill>
-                <a:effectLst>
-                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                    <a:prstClr val="black">
-                      <a:alpha val="40000"/>
-                    </a:prstClr>
-                  </a:outerShdw>
-                </a:effectLst>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -5796,7 +5774,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -5913,7 +5890,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -5986,7 +5962,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6148,29 +6123,18 @@
               <a:buFontTx/>
               <a:buNone/>
               <a:tabLst/>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:defRPr>
                 <a:solidFill>
                   <a:sysClr val="window" lastClr="FFFFFF">
                     <a:lumMod val="95000"/>
                   </a:sysClr>
                 </a:solidFill>
-                <a:effectLst>
-                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                    <a:prstClr val="black">
-                      <a:alpha val="40000"/>
-                    </a:prstClr>
-                  </a:outerShdw>
-                </a:effectLst>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7563,7 +7527,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -7680,7 +7643,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -7753,7 +7715,6 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
-      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7915,22 +7876,12 @@
               <a:buFontTx/>
               <a:buNone/>
               <a:tabLst/>
-              <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:defRPr>
                 <a:solidFill>
                   <a:sysClr val="window" lastClr="FFFFFF">
                     <a:lumMod val="95000"/>
                   </a:sysClr>
                 </a:solidFill>
-                <a:effectLst>
-                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
-                    <a:prstClr val="black">
-                      <a:alpha val="40000"/>
-                    </a:prstClr>
-                  </a:outerShdw>
-                </a:effectLst>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -59124,6 +59075,13 @@
       <c r="C205">
         <v>0.63301430000137704</v>
       </c>
+      <c r="E205" t="s">
+        <v>59</v>
+      </c>
+      <c r="F205">
+        <f>E203-F203</f>
+        <v>-0.14116532699985318</v>
+      </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206">
@@ -64760,6 +64718,13 @@
       <c r="C205">
         <v>0.93570229999750099</v>
       </c>
+      <c r="E205" t="s">
+        <v>61</v>
+      </c>
+      <c r="F205">
+        <f>E203-F203</f>
+        <v>-0.17464554650017827</v>
+      </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206">
@@ -70397,6 +70362,13 @@
       <c r="C206">
         <v>0.96744980000000003</v>
       </c>
+      <c r="E206" t="s">
+        <v>59</v>
+      </c>
+      <c r="F206">
+        <f>F204-G204</f>
+        <v>-0.22380513933955481</v>
+      </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207">
@@ -76018,6 +75990,13 @@
       <c r="C205">
         <v>0.89835160000075098</v>
       </c>
+      <c r="E205" t="s">
+        <v>60</v>
+      </c>
+      <c r="F205">
+        <f>F203-G203</f>
+        <v>-8.0642908541737057E-2</v>
+      </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206">
@@ -81616,6 +81595,9 @@
       <c r="C203">
         <v>0.96754999998665803</v>
       </c>
+      <c r="E203" t="s">
+        <v>58</v>
+      </c>
       <c r="F203">
         <f>AVERAGE(F2:F201)</f>
         <v>0.69775799999988464</v>
@@ -81645,6 +81627,13 @@
       </c>
       <c r="C205">
         <v>0.82396749999315899</v>
+      </c>
+      <c r="E205" t="s">
+        <v>59</v>
+      </c>
+      <c r="F205">
+        <f>F203-G203</f>
+        <v>-0.10942750357158815</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
